--- a/Bon_commande_mouser.xlsx
+++ b/Bon_commande_mouser.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gokay\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antotauv\Documents\Projet_1A_2026\ENSEA_S6_PROJET_OSCILLO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6B1BD70-C016-4321-B18E-F3E6CA1A4732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91413A0A-058A-484B-A494-27117D213A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C464CEEC-08DB-48F4-806D-00D034909B91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C464CEEC-08DB-48F4-806D-00D034909B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Mouser</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>TA.01</t>
-  </si>
-  <si>
-    <t>Frais de port et de livraison</t>
   </si>
   <si>
     <t>Pos</t>
@@ -242,10 +239,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -583,59 +580,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1619B74D-FFFB-4810-8708-F6BF00100D65}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>10</v>
       </c>
@@ -643,12 +640,12 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="7">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6">
         <v>1</v>
       </c>
-      <c r="I3" s="7"/>
+      <c r="I3" s="6"/>
       <c r="J3" t="s">
         <v>2</v>
       </c>
@@ -665,7 +662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>20</v>
       </c>
@@ -673,12 +670,12 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="6">
+        <v>19</v>
+      </c>
+      <c r="H4" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="7"/>
       <c r="J4" t="s">
         <v>2</v>
       </c>
@@ -695,20 +692,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>30</v>
+      </c>
       <c r="B5" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Bon_commande_mouser.xlsx
+++ b/Bon_commande_mouser.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antotauv\Documents\Projet_1A_2026\ENSEA_S6_PROJET_OSCILLO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gokay\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91413A0A-058A-484B-A494-27117D213A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8DB5382-10A9-456B-9BBB-5F6AE654EF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C464CEEC-08DB-48F4-806D-00D034909B91}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{C464CEEC-08DB-48F4-806D-00D034909B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Mouser</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Connecteurs RF / Connecteurs coaxiaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frais de livraison </t>
+  </si>
+  <si>
+    <t>20 EUR</t>
   </si>
 </sst>
 </file>
@@ -146,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -185,19 +191,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -224,7 +217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -233,13 +226,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -580,15 +570,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1619B74D-FFFB-4810-8708-F6BF00100D65}">
-  <dimension ref="A1:P5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -601,38 +591,35 @@
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="J2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10</v>
       </c>
@@ -642,27 +629,26 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6">
+      <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="I3" s="6"/>
+      <c r="G3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>8.6</v>
+      </c>
       <c r="J3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" t="s">
         <v>2</v>
       </c>
-      <c r="L3">
-        <v>8.6</v>
-      </c>
-      <c r="M3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="L3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20</v>
       </c>
@@ -672,41 +658,34 @@
       <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="7">
+      <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="G4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3.88</v>
+      </c>
       <c r="J4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
         <v>2</v>
       </c>
-      <c r="L4">
-        <v>3.88</v>
-      </c>
-      <c r="M4" t="s">
-        <v>3</v>
-      </c>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="L4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1</v>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>